--- a/artfynd/A 55051-2021 artfynd.xlsx
+++ b/artfynd/A 55051-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55051-2021 artfynd.xlsx
+++ b/artfynd/A 55051-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54011241</v>
+        <v>93442596</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6436</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harvik, 1,0 km SV-ut, Upl</t>
+          <t>Dannemorasjön NO, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658486.1342028844</v>
+        <v>658808</v>
       </c>
       <c r="R2" t="n">
-        <v>6675057.192074942</v>
+        <v>6675445</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,37 +757,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Benny Willman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Benny Willman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54011238</v>
+        <v>93442615</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,38 +802,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>6443</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harvik, 1,0 km SV-ut, Upl</t>
+          <t>Dannemorasjön NO, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658462.9004908428</v>
+        <v>658808</v>
       </c>
       <c r="R3" t="n">
-        <v>6675052.201117095</v>
+        <v>6675445</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,76 +873,91 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Benny Willman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Benny Willman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54011240</v>
+        <v>13545231</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>201143</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Harvik, 1,0 km SV-ut, Upl</t>
+          <t>träbron och gläntan söder om Dalån, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658486.1342028844</v>
+        <v>658495</v>
       </c>
       <c r="R4" t="n">
-        <v>6675057.192074942</v>
+        <v>6675023</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +981,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,70 +1011,79 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Oskar Kindvall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Oskar Kindvall, olle kindvall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54011239</v>
+        <v>13545203</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>201146</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Harvik, 1,0 km SV-ut, Upl</t>
+          <t>Glänta, N Dalån, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658462.9004908428</v>
+        <v>658595</v>
       </c>
       <c r="R5" t="n">
-        <v>6675052.201117095</v>
+        <v>6675024</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1107,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-13</t>
+          <t>2008-07-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1137,419 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Oskar Kindvall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Oskar Kindvall, olle kindvall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>54011240</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Harvik, 1,0 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>658486</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6675057</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Henry Åkerström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>54011239</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Harvik, 1,0 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>658463</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6675052</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54011241</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Harvik, 1,0 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>658486</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6675057</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>54011238</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Harvik, 1,0 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>658463</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6675052</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-06-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>

--- a/artfynd/A 55051-2021 artfynd.xlsx
+++ b/artfynd/A 55051-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93442596</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93442615</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13545231</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13545203</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54011240</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54011239</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54011241</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,8 +1594,23 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54011238</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>